--- a/java-projects/maven/maven-projects/aggregator/youtube/author-javatechie/link-javatechie.xlsx
+++ b/java-projects/maven/maven-projects/aggregator/youtube/author-javatechie/link-javatechie.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace_labs_intellij_java/parent-java/java-projects/maven/maven-projects/aggregator/youtube/author-amigoscode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace_labs_intellij_java/parent-java/java-projects/maven/maven-projects/aggregator/youtube/author-javatechie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CDBA83-2101-7B43-B4C6-03378F606DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2752C445-7022-984D-B617-D67EC4F2AB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="1220" windowWidth="28000" windowHeight="17160" xr2:uid="{F2BF7380-C660-9E42-8412-3FCAAAAB8BB5}"/>
+    <workbookView xWindow="1680" yWindow="7400" windowWidth="28000" windowHeight="17160" activeTab="1" xr2:uid="{F2BF7380-C660-9E42-8412-3FCAAAAB8BB5}"/>
   </bookViews>
   <sheets>
-    <sheet name="amigoscode" sheetId="1" r:id="rId1"/>
+    <sheet name="javatechie" sheetId="1" r:id="rId1"/>
+    <sheet name="javatechie-course-ongraphy" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">amigoscode!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">javatechie!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Sr</t>
   </si>
@@ -50,67 +51,25 @@
     <t>links</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=8MmMm2-kJV8</t>
-  </si>
-  <si>
-    <t>Java Data Structures Tutorial</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Qgl81fPcLc8</t>
-  </si>
-  <si>
-    <t>Java Full Course [NEW]</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=VRpHdSFWGPs</t>
-  </si>
-  <si>
-    <t>Java Functional Programming | Full Course</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=8SGI_XS5OPw</t>
-  </si>
-  <si>
-    <t>Spring Boot Tutorial | Spring Data JPA | 2021</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=b9O9NI-RJ3o</t>
-  </si>
-  <si>
-    <t>Spring Security Tutorial - [NEW] [2023]</t>
-  </si>
-  <si>
-    <t>Spring Security 7 Crash Course [2026] – Everything You Need to Know</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=IqW6NVxPaTc</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Geq60OVyBPg</t>
-  </si>
-  <si>
-    <t>Software Testing Tutorial - Learn Unit Testing and Integration Testing</t>
-  </si>
-  <si>
     <t>Project Name</t>
   </si>
   <si>
-    <t>amigoscode-data-structures</t>
-  </si>
-  <si>
-    <t>amigoscode-java-full-course</t>
-  </si>
-  <si>
-    <t>amigoscode-java-functional-programming</t>
-  </si>
-  <si>
-    <t>amigoscode-java-spring-boot-spring-data-jpa</t>
-  </si>
-  <si>
-    <t>amigoscode-java-spring-security</t>
-  </si>
-  <si>
-    <t>amigoscode-java-unit-testing-and-integration-testing</t>
+    <t>github</t>
+  </si>
+  <si>
+    <t>https://github.com/Java-Techie-jt/api-versioning</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SUfYMpWXJ7g</t>
+  </si>
+  <si>
+    <t>Spring Boot 4 API Versioning – Stop Breaking Client APIs</t>
+  </si>
+  <si>
+    <t>jt-api-versioning</t>
+  </si>
+  <si>
+    <t>https://github.com/orgs/SpringBoot-javatechie/repositories</t>
   </si>
 </sst>
 </file>
@@ -500,16 +459,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0315C447-8243-764B-A149-52A5803FFBCD}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="57.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,124 +477,158 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{0315C447-8243-764B-A149-52A5803FFBCD}"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{2A8A7EA5-E704-CA4E-A27C-FB0DE5D07C8A}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{7F80C0E5-8126-6A4B-B4DE-4F1F4369FBAE}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{3FDB69C6-DE70-0648-A011-3C7C14751467}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{CD5C5781-AC48-C341-B47C-AF7031AAD710}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{3EF1F700-795D-B549-B801-A83A5AF6EACC}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{46B0846A-FAF4-824B-AD09-EB4424EAF363}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{86262A7F-AB31-1343-889C-B8A117CF9CE5}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{5986519A-E177-FD45-955B-A19D872F166A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E275E9F2-E722-A449-9240-03D6C407BD7D}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>